--- a/artfynd/A 5360-2022 artfynd.xlsx
+++ b/artfynd/A 5360-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 5360-2022 artfynd.xlsx
+++ b/artfynd/A 5360-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16773781</v>
+        <v>16773783</v>
       </c>
       <c r="B2" t="n">
-        <v>83136</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3518</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smal svampklubba</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tolypocladium ophioglossoides</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Knutatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469767.4809925634</v>
+        <v>469833</v>
       </c>
       <c r="R2" t="n">
-        <v>6625682.028100899</v>
+        <v>6625661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,19 +746,9 @@
           <t>2014-10-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-10-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,13 +757,12 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskog i 40-50-års-åldern på igenväxt åkerteg.</t>
+          <t>I övergången mellan fastmark och sumpskog vid laggen av Knuthöjdsmossen.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -803,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16773783</v>
+        <v>16773781</v>
       </c>
       <c r="B3" t="n">
-        <v>93044</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,37 +791,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2809</v>
+        <v>3518</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Smal svampklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Tolypocladium ophioglossoides</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Ehrh. ex J.F.Gmel.:Fr.) Quandt, Kepler &amp; Spatafora</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Knutatorpet, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469832.905822708</v>
+        <v>469767</v>
       </c>
       <c r="R3" t="n">
-        <v>6625660.844765509</v>
+        <v>6625682</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,19 +858,9 @@
           <t>2014-10-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-10-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,12 +869,13 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>I övergången mellan fastmark och sumpskog vid laggen av Knuthöjdsmossen.</t>
+          <t>Granskog i 40-50-års-åldern på igenväxt åkerteg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 5360-2022 artfynd.xlsx
+++ b/artfynd/A 5360-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16773783</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,8 +900,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16773781</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>